--- a/extenbooks/S703.xlsx
+++ b/extenbooks/S703.xlsx
@@ -537,10 +537,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>benchmark_only</t>
+          <t>derived</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1947–1977</t>
+          <t>1947-1977</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_sourcing</t>
+          <t>benchmark_only_matrix_derived</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_7_1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,134 +702,156 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PROXY DISCLOSURE</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>proxy_disclosure</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Matrix-derived or surrogate construction; consult docs/series/S703_DPR.md for full disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S703-A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S703 — Value-Price Deviations — PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Content Type**: benchmark_only</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Units**: percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S703 — Value-Price Deviations (PROXY)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Chapter 7's percent deviation between labor values (S701) and prices of production (S702). The book's central finding: deviations small but systematic — labor value is a good first approximation to price.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- **SID**: S703</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>depends on S701 and S702</t>
+          <t>- **Name**: Value-Price Deviations (Chapter 7 R² regression — currently implemented as percent-deviation PROXY)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 7; registry book_table label "7.3" is project-internal — the book's actual Table 7.3 does not exist as a printed table. The empirical anchor is Khanjian 1989 (6-9% S*/V* deviation) reported in Ch7 §7.3 (p.223) and the consistent-procedure framework in Ch4 §4.1 Tables 4.1-4.3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Acceptance criteria for activation</t>
+          <t>- **Status**: `benchmark_only_matrix_derived` with `proxy: true` (six SIC benchmark years)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>- **Units**: percent (deviation of S702 from S701)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- [ ] Activate S701 and S702</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- [ ] Compute (S702 - S701) / S701 * 100</t>
+          <t>## Methodology — PROXY DISCLOSURE</t>
         </is>
       </c>
     </row>
@@ -837,7 +863,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Faithfulness considerations</t>
+          <t>**S703 is currently a percent-deviation PROXY: `(S702 − S701) / S701 × 100`. The book's actual specification is a cross-sectional log-log OLS regression of total labor values against total prices of production across productive sectors, run separately per benchmark year, with the R² statistic interpreted as an empirical test of the labor theory of value. The current single-scalar deviation cannot perform that test; the proxy preserves only the qualitative finding of systematic positive deviation.**</t>
         </is>
       </c>
     </row>
@@ -849,7 +875,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>When activated, the loader must use the same agency/table the book used (BEA Benchmark I-O for matrix series; BLS CES for sectoral employment). No proxy substitutions per the Anu Extension Standard.</t>
+          <t>The book's framework is a "consistent procedure" — sector-disaggregated labor values from `lambda* = hp* · (I - A*)^{-1}` and sector-disaggregated prices of production from `pp*_j = (1 + r̄)(c_j_labor + v_j_labor)` — under which deviations between value and money ratios can be interpreted as the empirical effect of price-value deviations. The verbatim setup is: **"All these mappings were constructed on the assumption that purchasers' prices were proportional to labor values. This allowed us to check that the various elements add up to the correct totals, no matter how complicated the transfers of value involved. It also ensured that any discrepancies that arose between individual Marxian categories and their orthodox counterparts were due solely to conceptual differences, not to any price-value deviations that might exist."** (ST 1994 Ch7 §7.3, p.223); and: **"In Chapter 4 we extend the analysis to the calculation of actual labor value magnitudes. We show that the correct procedure is consistent, in the sense that it gives the same ratios in value terms and in price terms when unit purchaser prices are equal to unit values (Tables 4.1 and 4.2). This means that in actual input-output tables, where purchasers' prices generally do differ from values, we can then interpret the deviations between value and money ratios as a measure of the aggregate effects of price-value deviations, if the procedure used is consistent in the sense just described."** (ST 1994 Ch7 §7.3, p.223). The headline empirical claim, due to Khanjian: **"Using the consistent procedure, Khanjian (1989) shows that value and price rates of surplus value differ by only small amounts (6%-9%), which indicates that the effects of price-value deviations on aggregate measures are quite minor (Section 5.10, Table 5.12, and Figure 5.25)."** (ST 1994 Ch7 §7.3, p.223). The contrast with Wolff is also explicit: an inconsistent (symmetric) procedure biases the money rate S*/V* upward by 12-15% (sum of Wolff's 4-8% and Khanjian's 6-9%).</t>
         </is>
       </c>
     </row>
@@ -861,7 +887,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>The current S703 implementation computes a single scalar percent deviation per benchmark year. Observed range is [35.5%, 41.8%] over the six benchmark years — much larger than the book's 6-9% Khanjian benchmark because the proxy inherits both upstream proxies (S701 lacks `hp*`; S702 applies a single aggregate `λ_m` and uses GO−V* surplus). The proxy preserves the qualitative book finding of systematic positive price-value deviation but cannot empirically test the labor theory of value as the book intends. The verbatim disclosure anchor is the inconsistent-procedure diagnosis: **"Inconsistent (symmetric) procedure (pages 85-86): how it arises — tempting to make price form symmetric with value form. … False symmetry: treats trade sector like royalties sector ('both unproductive'). Result: estimated money magnitudes smaller than value ones, even when prices = values. Inconsistent procedure biases each money magnitude downward by trading margin amount."** (ST 1994 Ch4 §4.1 Table 4.3, pp.85-86). This matches the observed S703 failure pattern: R² collapsed to 0.003-0.035 before a `λ_m` scaling fix, improved to 0.70-0.98 after — still short of the implied book R² &gt; 0.95 because the underlying procedure is inconsistent in the book's technical sense.</t>
         </is>
       </c>
     </row>
@@ -873,7 +899,311 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (pending DPR; activate when prerequisites are met).*</t>
+          <t>The real fix mirrors the S701/S702 real fix: source `hp*_j` per sector from BLS productive-employment hours times average weekly hours divided by sector gross output in producer prices (Appendix G Table G.2 enumerates the 8 sectors); construct sector-level `c_j` and `v_j` via `lambda_i* · (M_p)_p` and `lambda* · (CONW_p)_p` per Ch4 §4.1; then run the actual cross-sectional regression `log(lambda_j) ~ log(pp*_j)` per benchmark year and report R². The expected R² range under a consistent procedure is implied to be &gt; 0.90 (the book does not literally claim R² &gt; 0.95 in Ch7; the prior project research file's attribution of that exact figure has been flagged for re-verification). The 1963 benchmark anomaly (WARN-03) — S702 collapsing to near-zero, S701 dropping to 0.00037 — is the most likely driver of any single-year R² outlier and must be diagnosed (likely a 1963 BEA IO data gap) before the regression results are reportable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 Tables 4.1-4.3 — consistent/inconsistent procedure); `chunk_25/full_transcription.md` (Ch7 §7.3-§7.4 — Khanjian 6-9% benchmark, Wolff 12-15% bias); `chunk_33/full_transcription.md` (Appendix G intro + Table G.1 V* methodology); `chunk_34/full_transcription.md` (Appendix G Table G.2 V* formulas); `chunk_36/full_transcription.md` (Appendix J C*/TP* stability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- Book tables: Ch4 §4.1 Tables 4.1, 4.2, 4.3 (consistent vs inconsistent procedure worked examples); Section 5.10 Table 5.12 (Khanjian comparison); Section 5.10 Figure 5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- External sources: Khanjian (1988, p.109 table 19; 1989) — the 6-9% benchmark; Wolff (1977a/b; 1979; 1987) — the symmetric-treatment comparator; Sharpe (1982) — same family of biased treatments</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- Upstream series: S701 (labor values proxy), S702 (prices of production proxy), S513 (Marxian profit rate, used in S702)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- Local files: `data/final/S701.csv`, `data/final/S702.csv`; printed-book digitization placeholder at `data/source/book_tables/ch07/Table7_3_ValuePriceDeviations.csv` (not yet populated; book table does not actually exist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- Observed proxy deviation range: `[35.5%, 41.8%]` (single scalar percent per year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- Validator `expected_range`: `[0.0, 100.0]` (accepts the proxy's wide range; not the book's intended 6-9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- **Book's Khanjian benchmark**: 6-9% deviation in S*/V* between price and value forms (Ch7 §7.3, p.223)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- **Book's Wolff comparator**: 12-15% upward bias in money S*/V* from inconsistent symmetric procedure (Ch7 §7.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- The book does NOT literally claim R² &gt; 0.95 in Ch7; the prior research file's attribution of that exact figure is flagged for re-verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- Current ST2-era implementation R² (after `λ_m` fix): 0.70-0.98 per benchmark year — still short of the consistent-procedure benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- **Proxy implementation flagged `proxy: true`**: single percent-deviation scalar substitutes for the book's cross-sectional log-log regression; cannot produce R²</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- **Inherits both upstream proxies**: S701 lacks `hp*`; S702 uses single aggregate `λ_m` and GO−V* surplus error</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- **Magnitudes ~5x book**: observed 35.5-41.8% vs book's 6-9% Khanjian benchmark — symptomatic of the inconsistent procedure diagnosed in Ch4 §4.1 Table 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- **R² gap in ST2 implementation (0.70-0.98 vs implied &gt;0.90)**: gap is driven by scalar λ_m and GO−V* surplus error, not by a real failure of the labor theory of value</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- **1963 benchmark anomaly (WARN-03)**: drives single-year R² outliers; likely IO data gap; not yet diagnosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- **Only 6 benchmark years available**: small cross-section limits regression robustness even when the real fix is implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- **Sector-level value-added decomposition (ST 1994 §4.2 pp.86-88) not yet implemented**: current code uses aggregate scalar ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- **Book R²&gt;0.95 attribution unverified**: prior research files assert this but direct re-read of Ch7 finds no such literal claim; the load-bearing book number is Khanjian's 6-9%, not 95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- **CH7_REAL_FIX_PLAN.md not yet authored** — flagged here as "to be authored alongside Stage 5 real-fix sub-stage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- Upstream: S701 (labor values), S702 (prices of production), S513 (Marxian profit rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- Downstream: none (S703 is the empirical test endpoint of the Ch7 framework)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- Related external: Khanjian (1988, 1989), Wolff (1977a/b, 1979, 1987), Sharpe (1982); the book's Ch7 §7.4 cross-study critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- Project artifact: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` (to be authored); WARN-03 1963 diagnosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 11/25/33/34/36 cited via research JSON + registry entry + project CLAUDE.md proxy-disclosure mandate</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -888,7 +1218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -916,245 +1246,437 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S703 implements a cross-sectional log-log OLS regression of total labor values against total prices of production across productive sectors, run separately for each IO benchmark year (1947, 1958, 1963, 1967, 1972, 1977). The regression formula is: log(total_labor_values_j) = α + β · log(total_prices_of_production_j) + ε_j, where j indexes productive sectors. R² from this regression measures how well labor values predict market prices, providing an empirical test of the labor theory of value. The book (Shaikh &amp; Tonak 1994, Ch. 7, Table 7.3) claims R² &gt; 0.95 across benchmark years, interpreted as strong confirmation that labor values are the dominant determinant of relative prices of production.</t>
+          <t>All these mappings were constructed on the assumption that purchasers' prices were proportional to labor values. This allowed us to check that the various elements add up to the correct totals, no matter how complicated the transfers of value involved. It also ensured that any discrepancies that arose between individual Marxian categories and their orthodox counterparts were due solely to conceptual differences, not to any price-value deviations that might exist.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch7, Table 7.3; series_registry.json S703 entry</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S703 is derived from S701 (labor values λ* in hours per dollar) and S702 (prices of production pp* in labor-value terms). Sector-level total labor values are computed as S701 × gross output for each productive sector at each IO benchmark year. Sector-level total prices of production come from S702 using the price-of-production formula pp*_j = (1 + r̄)(c_j_labor + v_j_labor), where r̄ is the uniform profit rate and c_j_labor, v_j_labor are constant and variable capital expressed in labor-value units via the labor value of money λ_m = total productive hours / total value added. The regression is then run cross-sectionally across productive sectors at each benchmark year. Book subseries S703-A covers 1947–1977 (6 benchmark years) and is loaded from ch07/Table7_3_ValuePriceDeviations.csv.</t>
+          <t>In Chapter 4 we extend the analysis to the calculation of actual labor value magnitudes. We show that the correct procedure is consistent, in the sense that it gives the same ratios in value terms and in price terms when unit purchaser prices are equal to unit values (Tables 4.1 and 4.2). This means that in actual input-output tables, where purchasers' prices generally do differ from values, we can then interpret the deviations between value and money ratios as a measure of the aggregate effects of price-value deviations, if the procedure used is consistent in the sense just described.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>series_registry.json S703, S701, S702 entries; DEC-011</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>variable_capital_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Variable capital V* (a key input to the price-of-production formula) is estimated in the book (Appendix G, Tables G.1–G.2) from BLS production worker wages (wp) scaled by the NIPA employee-compensation-to-wages ratio x = EC/WS, then multiplied by productive employment Lp: V*_j = (wp_j × x_j × 52) × (Lp)_j. This procedure effectively excludes corporate officers' salaries from V*. Because BLS does not publish separate wage rates for nonproduction workers, unproductive wages Wu = W − V* are derived residually. The productivity appendix (Appendix J) confirms that C*/TP* is empirically stable, implying y* and q* track closely — a stability that also underpins the price-of-production computation by keeping the composition of capital (C*/VA*) well-behaved across sectors.</t>
+          <t>Wolff treats money and labor value calculations symmetrically, which makes the former inconsistent with the latter. Indeed, as expected on theoretical grounds, Wolff's estimates of money rates of surplus value are uniformly higher than his labor value estimates by about 4%-8% (Wolff 1977b, p. 103, table 3, lines 1 and 3). On the other hand, Khanjian's estimates indicate that S*/V* is uniformly lower than S/V by about 6%-9% (Khanjian 1988, p. 109, table 19). This allows us to estimate that Wolff's inconsistent procedure biases the money rate of surplus value S*/V* upward by 12%-15% (the sum of the two sets of differences in years common to both Khanjian and Wolff).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chunk_33 (Appendix G intro, Table G.1); chunk_34 (Table G.2, V* formulas); chunk_36 (Appendix J, C*/TP* stability)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit_conversion_requirement</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Correct computation of S703 requires that labor values and prices of production be expressed in commensurable units before regression. Labor values λ* are in hours per dollar of gross output; prices of production in money terms are in dollars. The conversion uses the labor value of money λ_m = total productive hours / total value added. Money compensation v_j is converted to labor-value compensation v_j_labor = v_j × λ_m before computing pp*_j. The initial ST2 implementation omitted this conversion, producing R² = 0.003–0.035 and MAD &gt; 31,000%. After applying the λ_m conversion, MAD improved to 72–87% but R² remained low (0.003–0.035), indicating a residual methodological issue: surplus was computed from gross output minus V* rather than value added minus V*, contrary to the book's Section 4.2 (pp. 86–88) sector-level value-added decomposition.</t>
+          <t>Using the consistent procedure, Khanjian (1989) shows that value and price rates of surplus value differ by only small amounts (6%-9%).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEC-011 (2026-04-09 and update)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEC-011 documents three layers of the R² inconsistency: (1) the λ_m scalar conversion is applied uniformly across all sectors (same scalar V*/VA* ratio for all j), whereas the book implies sector-level value-added decomposition; (2) the 1963 IO benchmark year shows anomalous S701 and S702 values (S702 near floating-point zero at 1963, S701 dropping to 0.00037 before jumping to 0.036 in 1964), suggesting a data quality issue at that benchmark — designated WARN-03; (3) the regression spans only 6 IO benchmark years (1947, 1958, 1963, 1967, 1972, 1977), limiting statistical power and making R² sensitive to individual outlier years. The 1963 anomaly is the most likely driver of the low R² results in benchmark years near that point.</t>
+          <t>Definition of consistent mapping: Tables 4.1 and 4.2 are CONSISTENT -- they give same magnitudes in value and price terms when unit purchaser prices = unit values. Purpose: when prices deviate from values, discrepancies between value and money magnitudes are due SOLELY to price-value deviations themselves. Empirical evidence (Khanjian 1989:109, table 19): money rate S*/V* and labor value rate S/V differ by only 6%-9% in all years studied; S*/V* consistently lower than S/V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEC-011; NickyData/data/final-data/book/series/S701.csv; NickyData/data/final-data/book/series/S702.csv; ASSUMPTIONS.md ASM-M-002</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>known_issues</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Current ST2 implementation achieves R² = 0.70–0.98 (varies by benchmark year) versus the book's claim of R² &gt; 0.95. The gap is caused by: (a) scalar rather than sector-level λ_m application — the book requires computing c_j and v_j in labor-value units sector by sector, not applying a single aggregate ratio; (b) incorrect surplus computation using GO − V* instead of VA − V* in the profit-rate equalization step; (c) the 1963 benchmark anomaly (WARN-03) where S702 collapses to near-zero values, likely reflecting a data gap in the underlying IO table rather than a true economic reading. Resolution is deferred to Wave 2, pending a dedicated sector-level value-added decomposition pass and diagnosis of the 1963 IO data.</t>
+          <t>Inconsistent (symmetric) procedure (pages 85-86): how it arises -- tempting to make price form symmetric with value form. Since value calculations use ONLY producer prices: NP = V = lambda* * (CONWp)_p. One might mistakenly use ONLY producer prices for money calculations too: NP*' = (CONWp)_p (WRONG! Omits trading margin). Correct money form: NP* = CONWp = (CONWp)_p + (CONWp)_t. False symmetry: treats trade sector like royalties sector ('both unproductive'). Result: estimated money magnitudes smaller than value ones, even when prices = values. Inconsistent procedure biases each money magnitude downward by trading margin amount.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEC-011; series_registry.json S703 (wave: 2, status: calculated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>For production sector j, let lambda_j = labor value per unit output; hp_j = hours of productive labor per unit output; app_ij = quantity of the ith production input used per unit output. Then unit labor values must satisfy the relation lambda_j = hp_j + sum_i lambda_i * app_ij. Unit labor value = Direct labor hours + Labor value embodied in inputs. Recursive definition requiring simultaneous solution.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S703 is a cross-sectional log-log R² regression of total labor values vs. total prices of production across productive sectors at each IO benchmark year (1947, 1958, 1963, 1967, 1972, 1977). The book reports R² &gt; 0.95, interpreted as empirical confirmation of the labor theory of value. Current implementation achieves R² = 0.70–0.98 due to scalar (not sector-level) λ_m application and incorrect surplus computation; resolution deferred to Wave 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>S703 implements a cross-sectional log-log OLS regression of total labor values against total prices of production across productive sectors, run separately for each IO benchmark year (1947, 1958, 1963, 1967, 1972, 1977). The regression formula is: log(total_labor_values_j) = α + β · log(total_prices_of_production_j) + ε_j, where j indexes productive sectors. R² from this regression measures how well labor values predict market prices, providing an empirical test of the labor theory of value. The book (Shaikh &amp; Tonak 1994, Ch. 7, Table 7.3) claims R² &gt; 0.95 across benchmark years, interpreted as strong confirmation that labor values are the dominant determinant of relative prices of production.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch7, Table 7.3; series_registry.json S703 entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S703 is derived from S701 (labor values λ* in hours per dollar) and S702 (prices of production pp* in labor-value terms). Sector-level total labor values are computed as S701 × gross output for each productive sector at each IO benchmark year. Sector-level total prices of production come from S702 using the price-of-production formula pp*_j = (1 + r̄)(c_j_labor + v_j_labor), where r̄ is the uniform profit rate and c_j_labor, v_j_labor are constant and variable capital expressed in labor-value units via the labor value of money λ_m = total productive hours / total value added. The regression is then run cross-sectionally across productive sectors at each benchmark year. Book subseries S703-A covers 1947–1977 (6 benchmark years) and is loaded from ch07/Table7_3_ValuePriceDeviations.csv.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>series_registry.json S703, S701, S702 entries; [internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>variable_capital_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Variable capital V* (a key input to the price-of-production formula) is estimated in the book (Appendix G, Tables G.1–G.2) from BLS production worker wages (wp) scaled by the NIPA employee-compensation-to-wages ratio x = EC/WS, then multiplied by productive employment Lp: V*_j = (wp_j × x_j × 52) × (Lp)_j. This procedure effectively excludes corporate officers' salaries from V*. Because BLS does not publish separate wage rates for nonproduction workers, unproductive wages Wu = W − V* are derived residually. The productivity appendix (Appendix J) confirms that C*/TP* is empirically stable, implying y* and q* track closely — a stability that also underpins the price-of-production computation by keeping the composition of capital (C*/VA*) well-behaved across sectors.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chunk_33 (Appendix G intro, Table G.1); chunk_34 (Table G.2, V* formulas); chunk_36 (Appendix J, C*/TP* stability)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>unit_conversion_requirement</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R² = 0.70–0.98 vs. book claim of R² &gt; 0.95 — gap driven by scalar λ_m application and GO−V* surplus error</t>
+          <t>Correct computation of S703 requires that labor values and prices of production be expressed in commensurable units before regression. Labor values λ* are in hours per dollar of gross output; prices of production in money terms are in dollars. The conversion uses the labor value of money λ_m = total productive hours / total value added. Money compensation v_j is converted to labor-value compensation v_j_labor = v_j × λ_m before computing pp*_j. The initial ST2 implementation omitted this conversion, producing R² = 0.003–0.035 and MAD &gt; 31,000%. After applying the λ_m conversion, MAD improved to 72–87% but R² remained low (0.003–0.035), indicating a residual methodological issue: surplus was computed from gross output minus V* rather than value added minus V*, contrary to the book's Section 4.2 (pp. 86–88) sector-level value-added decomposition.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09 and update)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1963 benchmark anomaly (WARN-03): S702 near-zero values at 1963, S701 discontinuity 1963→1964, likely IO data gap</t>
+          <t>[internal-decision-record] documents three layers of the R² inconsistency: (1) the λ_m scalar conversion is applied uniformly across all sectors (same scalar V*/VA* ratio for all j), whereas the book implies sector-level value-added decomposition; (2) the 1963 IO benchmark year shows anomalous S701 and S702 values (S702 near floating-point zero at 1963, S701 dropping to 0.00037 before jumping to 0.036 in 1964), suggesting a data quality issue at that benchmark — designated WARN-03; (3) the regression spans only 6 IO benchmark years (1947, 1958, 1963, 1967, 1972, 1977), limiting statistical power and making R² sensitive to individual outlier years. The 1963 anomaly is the most likely driver of the low R² results in benchmark years near that point.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]; NickyData/data/final-data/book/series/S701.csv; NickyData/data/final-data/book/series/S702.csv; ASSUMPTIONS.md ASM-M-002</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>known_issues</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Only 6 benchmark years available (1947, 1958, 1963, 1967, 1972, 1977) — small cross-section limits regression robustness</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sector-level value-added decomposition (ST 1994, Section 4.2, pp. 86–88) not yet implemented; current code uses aggregate scalar ratio</t>
-        </is>
-      </c>
-    </row>
+          <t>Current ST2 implementation achieves R² = 0.70–0.98 (varies by benchmark year) versus the book's claim of R² &gt; 0.95. The gap is caused by: (a) scalar rather than sector-level λ_m application — the book requires computing c_j and v_j in labor-value units sector by sector, not applying a single aggregate ratio; (b) incorrect surplus computation using GO − V* instead of VA − V* in the profit-rate equalization step; (c) the 1963 benchmark anomaly (WARN-03) where S702 collapses to near-zero values, likely reflecting a data gap in the underlying IO table rather than a true economic reading. Resolution is deferred to Wave 2, pending a dedicated sector-level value-added decomposition pass and diagnosis of the 1963 IO data.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]; series_registry.json S703 (wave: 2, status: calculated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Full resolution deferred to Wave 2 pending dedicated λ_m and VA* decomposition work</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S701</t>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>224</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S702</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DEC-011</t>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>WARN-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>85-86</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>methodology_summary</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BLS_SEHE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bureau of Labor Statistics. 1989. Supplement to Employment, Hours, and Earnings, United States, 1909-84. BLS Bulletin 1312-12.</t>
-        </is>
-      </c>
-    </row>
+          <t>S703 is a cross-sectional log-log R² regression of total labor values vs. total prices of production across productive sectors at each IO benchmark year (1947, 1958, 1963, 1967, 1972, 1977). The book reports R² &gt; 0.95, interpreted as empirical confirmation of the labor theory of value. Current implementation achieves R² = 0.70–0.98 due to scalar (not sector-level) λ_m application and incorrect surplus computation; resolution deferred to Wave 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>R² = 0.70–0.98 vs. book claim of R² &gt; 0.95 — gap driven by scalar λ_m application and GO−V* surplus error</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1963 benchmark anomaly (WARN-03): S702 near-zero values at 1963, S701 discontinuity 1963→1964, likely IO data gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Only 6 benchmark years available (1947, 1958, 1963, 1967, 1972, 1977) — small cross-section limits regression robustness</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sector-level value-added decomposition (ST 1994, Section 4.2, pp. 86–88) not yet implemented; current code uses aggregate scalar ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Full resolution deferred to Wave 2 pending dedicated λ_m and VA* decomposition work</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S701</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S702</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>WARN-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BLS_SEHE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bureau of Labor Statistics. 1989. Supplement to Employment, Hours, and Earnings, United States, 1909-84. BLS Bulletin 1312-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>BEA_NIPA_1986</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. 1986. National Income and Product Accounts of the United States, 1929-82. U.S. Department of Commerce.</t>
         </is>
@@ -1171,11 +1693,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1227,57 +1749,105 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PROXY CONSTRUCTION NOTICE</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>proxy_disclosure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
+          <t>Series is a proxy, not a direct replication. See DPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>null - series does not extend beyond book period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"1947": 37.77029651566801, "1958": 37.72037297739869, "1963": 41.520206844914256, "1967": 41.78590608470474, "1972": 37.77669655367616, "1977": 35.53064371634139}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[0.0, 100.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/extenbooks/S703.xlsx
+++ b/extenbooks/S703.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=percent</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 + BLS/BEA, units=percent</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES + BEA, units=percent</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -477,53 +489,547 @@
           <t>S703-A</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S703-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S703-EXT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1947</v>
+        <v>1967</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>37.77029651566801</v>
+        <v>-66.57979683368896</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>-66.57979683368896</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>37.72037297739869</v>
+        <v>-70.22495543814489</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-70.22495543814489</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1963</v>
+        <v>1977</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>41.52020684491426</v>
+        <v>-73.05320596603123</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-73.05320596603123</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1967</v>
+        <v>1990</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>41.78590608470474</v>
+        <v/>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-75.81705754778557</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-75.81705754778557</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1972</v>
+        <v>1991</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>37.77669655367616</v>
+        <v/>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-75.87627630063004</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-75.87627630063004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1977</v>
+        <v>1992</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>35.53064371634139</v>
+        <v/>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-75.85810335957103</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>-75.85810335957103</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-75.94073370266663</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-75.94073370266663</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-76.14499963452754</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-76.14499963452754</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-76.51253935478702</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-76.51253935478702</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-76.69317803046162</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>-76.69317803046162</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-76.78595994657277</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-76.78595994657277</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-76.70304576170466</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-76.70304576170466</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-76.5619511165565</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-76.5619511165565</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-76.90897819315325</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-76.90897819315325</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-76.95984863932946</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-76.95984863932946</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-76.48856120883886</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-76.48856120883886</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-76.27274568974205</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-76.27274568974205</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-76.57736033912896</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-76.57736033912896</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-76.836732033088</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-76.836732033088</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>-77.12039557550665</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-77.12039557550665</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-77.16677353425693</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-77.16677353425693</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-77.2586954182395</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-77.2586954182395</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-76.44613475528043</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-76.44613475528043</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-76.16159166835824</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>-76.16159166835824</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-76.50870872316462</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-76.50870872316462</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-76.72370779920013</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-76.72370779920013</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-76.88025728166258</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-76.88025728166258</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-77.21071331496849</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-77.21071331496849</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-77.30994877458866</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-77.30994877458866</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-77.33678016133159</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-77.33678016133159</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>-77.54479663202198</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-77.54479663202198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>-78.15106457725179</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>-78.15106457725179</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>-78.58800473957413</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-78.58800473957413</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-77.39133492145925</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-77.39133492145925</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-78.01836107779499</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-78.01836107779499</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>-79.19893212918043</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>-79.19893212918043</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>-80.09440933906036</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>-80.09440933906036</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>-80.61415861348353</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>-80.61415861348353</v>
       </c>
     </row>
   </sheetData>
@@ -537,10 +1043,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -648,7 +1154,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>benchmark_only_matrix_derived</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -704,110 +1210,113 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PROXY DISCLOSURE</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>S703-A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+          <t>S&amp;T 1994</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>proxy_basis</t>
+          <t>S703-EXT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>&lt;not specified&gt;</t>
+          <t>BLS CES + BEA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proxy_disclosure</t>
+          <t>S703-COMBINED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Matrix-derived or surrogate construction; consult docs/series/S703_DPR.md for full disclosure.</t>
+          <t>S&amp;T 1994 + BLS/BEA</t>
         </is>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Subseries</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>source / role</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DPR (markdown)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S703-A</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t># S703 — Value-Price Deviations (real, consistent-procedure regression)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DPR (markdown)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t># S703 — Value-Price Deviations (PROXY)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- **SID**: S703</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>## Series</t>
+          <t>- **Name**: Value-Price Deviations (Chapter 7 consistent-procedure regression; real implementation v1.1)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 7; registry `book_table` label "7.3" is project-internal — the book has no literal Table 7.3. The empirical anchor is Khanjian (1989) 6–9% S*/V* deviation reported in **Ch. 7 §7.3** (p.223) and the consistent-procedure framework in **Ch. 4 §4.1** Tables 4.1–4.3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **SID**: S703</t>
+          <t>- **Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -815,7 +1324,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Name**: Value-Price Deviations (Chapter 7 R² regression — currently implemented as percent-deviation PROXY)</t>
+          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
         </is>
       </c>
     </row>
@@ -823,23 +1332,19 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Chapter**: 7; registry book_table label "7.3" is project-internal — the book's actual Table 7.3 does not exist as a printed table. The empirical anchor is Khanjian 1989 (6-9% S*/V* deviation) reported in Ch7 §7.3 (p.223) and the consistent-procedure framework in Ch4 §4.1 Tables 4.1-4.3</t>
+          <t>- **Units**: percent (aggregate S*/V* deviation between price and value forms); also reports per-year R² from cross-sectional regression</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>- **Status**: `benchmark_only_matrix_derived` with `proxy: true` (six SIC benchmark years)</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- **Units**: percent (deviation of S702 from S701)</t>
+          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
         </is>
       </c>
     </row>
@@ -851,7 +1356,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Methodology — PROXY DISCLOSURE</t>
+          <t>S703 implements the book's consistent-procedure cross-sectional regression per ST 1994 Ch4 §4.1 + Ch7 §7.3 (p.223). The v1.0 percent-deviation scalar `(S702 - S701)/S701 * 100` (which was algebraically identical to S513 * 100 — see DIV-011 supersession note) has been retired. With both S701 and S702 now real and sector-disaggregated in v1.1, the book's empirical test is performed for the first time.</t>
         </is>
       </c>
     </row>
@@ -863,7 +1368,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>**S703 is currently a percent-deviation PROXY: `(S702 − S701) / S701 × 100`. The book's actual specification is a cross-sectional log-log OLS regression of total labor values against total prices of production across productive sectors, run separately per benchmark year, with the R² statistic interpreted as an empirical test of the labor theory of value. The current single-scalar deviation cannot perform that test; the proxy preserves only the qualitative finding of systematic positive deviation.**</t>
+          <t>Procedure (per `Technical/code/P02_processors/P02_S703_value_price_deviations.py`, v1.1 rewrite):</t>
         </is>
       </c>
     </row>
@@ -875,43 +1380,55 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The book's framework is a "consistent procedure" — sector-disaggregated labor values from `lambda* = hp* · (I - A*)^{-1}` and sector-disaggregated prices of production from `pp*_j = (1 + r̄)(c_j_labor + v_j_labor)` — under which deviations between value and money ratios can be interpreted as the empirical effect of price-value deviations. The verbatim setup is: **"All these mappings were constructed on the assumption that purchasers' prices were proportional to labor values. This allowed us to check that the various elements add up to the correct totals, no matter how complicated the transfers of value involved. It also ensured that any discrepancies that arose between individual Marxian categories and their orthodox counterparts were due solely to conceptual differences, not to any price-value deviations that might exist."** (ST 1994 Ch7 §7.3, p.223); and: **"In Chapter 4 we extend the analysis to the calculation of actual labor value magnitudes. We show that the correct procedure is consistent, in the sense that it gives the same ratios in value terms and in price terms when unit purchaser prices are equal to unit values (Tables 4.1 and 4.2). This means that in actual input-output tables, where purchasers' prices generally do differ from values, we can then interpret the deviations between value and money ratios as a measure of the aggregate effects of price-value deviations, if the procedure used is consistent in the sense just described."** (ST 1994 Ch7 §7.3, p.223). The headline empirical claim, due to Khanjian: **"Using the consistent procedure, Khanjian (1989) shows that value and price rates of surplus value differ by only small amounts (6%-9%), which indicates that the effects of price-value deviations on aggregate measures are quite minor (Section 5.10, Table 5.12, and Figure 5.25)."** (ST 1994 Ch7 §7.3, p.223). The contrast with Wolff is also explicit: an inconsistent (symmetric) procedure biases the money rate S*/V* upward by 12-15% (sum of Wolff's 4-8% and Khanjian's 6-9%).</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>per benchmark year y:</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The current S703 implementation computes a single scalar percent deviation per benchmark year. Observed range is [35.5%, 41.8%] over the six benchmark years — much larger than the book's 6-9% Khanjian benchmark because the proxy inherits both upstream proxies (S701 lacks `hp*`; S702 applies a single aggregate `λ_m` and uses GO−V* surplus). The proxy preserves the qualitative book finding of systematic positive price-value deviation but cannot empirically test the labor theory of value as the book intends. The verbatim disclosure anchor is the inconsistent-procedure diagnosis: **"Inconsistent (symmetric) procedure (pages 85-86): how it arises — tempting to make price form symmetric with value form. … False symmetry: treats trade sector like royalties sector ('both unproductive'). Result: estimated money magnitudes smaller than value ones, even when prices = values. Inconsistent procedure biases each money magnitude downward by trading margin amount."** (ST 1994 Ch4 §4.1 Table 4.3, pp.85-86). This matches the observed S703 failure pattern: R² collapsed to 0.003-0.035 before a `λ_m` scaling fix, improved to 0.70-0.98 after — still short of the implied book R² &gt; 0.95 because the underlying procedure is inconsistent in the book's technical sense.</t>
+          <t xml:space="preserve">  log(lambda*_j) ~ a_y + b_y * log(pp*_j)        # cross-sectional OLS across 8 ST productive sectors</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  R²_y = goodness of fit</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The real fix mirrors the S701/S702 real fix: source `hp*_j` per sector from BLS productive-employment hours times average weekly hours divided by sector gross output in producer prices (Appendix G Table G.2 enumerates the 8 sectors); construct sector-level `c_j` and `v_j` via `lambda_i* · (M_p)_p` and `lambda* · (CONW_p)_p` per Ch4 §4.1; then run the actual cross-sectional regression `log(lambda_j) ~ log(pp*_j)` per benchmark year and report R². The expected R² range under a consistent procedure is implied to be &gt; 0.90 (the book does not literally claim R² &gt; 0.95 in Ch7; the prior project research file's attribution of that exact figure has been flagged for re-verification). The 1963 benchmark anomaly (WARN-03) — S702 collapsing to near-zero, S701 dropping to 0.00037 — is the most likely driver of any single-year R² outlier and must be diagnosed (likely a 1963 BEA IO data gap) before the regression results are reportable.</t>
+          <t xml:space="preserve">  S*/V*_value(y), S*/V*_price(y) = aggregate rates of surplus value, value and price forms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  deviation_pct(y) = |S*/V*_price(y) - S*/V*_value(y)| / S*/V*_value(y) * 100</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -923,63 +1440,63 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 Tables 4.1-4.3 — consistent/inconsistent procedure); `chunk_25/full_transcription.md` (Ch7 §7.3-§7.4 — Khanjian 6-9% benchmark, Wolff 12-15% bias); `chunk_33/full_transcription.md` (Appendix G intro + Table G.1 V* methodology); `chunk_34/full_transcription.md` (Appendix G Table G.2 V* formulas); `chunk_36/full_transcription.md` (Appendix J C*/TP* stability)</t>
+          <t>The Khanjian (1989) 6–9% S*/V* envelope (ST 1994 Ch7 §7.3 p.223) is the load-bearing PASS/FAIL anchor; R² is a secondary diagnostic with small-cross-section caveats (8 productive sectors per benchmark year).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>- Book tables: Ch4 §4.1 Tables 4.1, 4.2, 4.3 (consistent vs inconsistent procedure worked examples); Section 5.10 Table 5.12 (Khanjian comparison); Section 5.10 Figure 5.25</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- External sources: Khanjian (1988, p.109 table 19; 1989) — the 6-9% benchmark; Wolff (1977a/b; 1979; 1987) — the symmetric-treatment comparator; Sharpe (1982) — same family of biased treatments</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>- Upstream series: S701 (labor values proxy), S702 (prices of production proxy), S513 (Marxian profit rate, used in S702)</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>- Local files: `data/final/S701.csv`, `data/final/S702.csv`; printed-book digitization placeholder at `data/source/book_tables/ch07/Table7_3_ValuePriceDeviations.csv` (not yet populated; book table does not actually exist)</t>
+          <t>- **L01 + P02 (real implementation)**: real S701 + S702 upstream (v1.1); `Technical/code/P02_processors/P02_S703_value_price_deviations.py` (v1.1 rewrite, runs cross-sectional regression and computes Khanjian-style aggregate deviation)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- **No new external data fetches required** — S703 is a pure regression on real upstream sector vectors</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>## Reference values</t>
+          <t>- **External comparator**: Khanjian (1989) "The Empirical Evidence Relating to the Existence of Prices of Production: A Critique of Wolff," *Review of Radical Political Economics*; serves as V03_S703 anchor</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 Tables 4.1-4.3 — consistent/inconsistent procedure); `chunk_25/full_transcription.md` (Ch7 §7.3–§7.4 — Khanjian 6–9%, Wolff 12–15% bias); `chunk_33/full_transcription.md` (Appendix G V* methodology); `chunk_34/full_transcription.md` (Appendix G Table G.2 V* formulas); `chunk_36/full_transcription.md` (Appendix J C*/TP* stability)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977</t>
+          <t>- **Book tables**: Ch4 §4.1 Tables 4.1, 4.2 (consistent procedure worked examples); Table 4.3 (inconsistent symmetric-treatment diagnosis); §5.10 Table 5.12, Figure 5.25 (Khanjian comparison)</t>
         </is>
       </c>
     </row>
@@ -987,71 +1504,67 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- Observed proxy deviation range: `[35.5%, 41.8%]` (single scalar percent per year)</t>
+          <t>- **Upstream series**: **S701 (real lambda* — v1.1)**, **S702 (real pp* — v1.1)**, S513 (Marxian profit rate r_bar, used in S702)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>- Validator `expected_range`: `[0.0, 100.0]` (accepts the proxy's wide range; not the book's intended 6-9%)</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- **Book's Khanjian benchmark**: 6-9% deviation in S*/V* between price and value forms (Ch7 §7.3, p.223)</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>- **Book's Wolff comparator**: 12-15% upward bias in money S*/V* from inconsistent symmetric procedure (Ch7 §7.4)</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- The book does NOT literally claim R² &gt; 0.95 in Ch7; the prior research file's attribution of that exact figure is flagged for re-verification</t>
+          <t>Coordinator backfills from `Technical/chopped/S703.csv` after agents 1-3 commit P02_S703 rewrite and `O01_generate_chopped.py` regenerates chopped output.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>- Current ST2-era implementation R² (after `λ_m` fix): 0.70-0.98 per benchmark year — still short of the consistent-procedure benchmark</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>- Extension years (NAICS): 1997, 2002, 2007, 2012 (per upstream S701/S702 NAICS benchmark availability)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>- **Khanjian benchmark**: 6–9% S*/V* deviation between price and value forms (ST 1994 Ch7 §7.3 p.223) — primary PASS/FAIL anchor</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- **Proxy implementation flagged `proxy: true`**: single percent-deviation scalar substitutes for the book's cross-sectional log-log regression; cannot produce R²</t>
+          <t>- **Wolff comparator**: 12–15% upper envelope (sum of Wolff 4–8% inconsistent-procedure bias + Khanjian 6–9% baseline)</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1572,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>- **Inherits both upstream proxies**: S701 lacks `hp*`; S702 uses single aggregate `λ_m` and GO−V* surplus error</t>
+          <t>- v1.1 `expected_range` tightened to `[0.0, 15.0]` (vs v1.0 proxy's `[0.0, 100.0]` that had to accept matrix-artifact range)</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1580,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- **Magnitudes ~5x book**: observed 35.5-41.8% vs book's 6-9% Khanjian benchmark — symptomatic of the inconsistent procedure diagnosed in Ch4 §4.1 Table 4.3</t>
+          <t>- Book does NOT literally claim R² &gt; 0.95 (prior research-file attribution flagged for re-verification); R² treated as secondary diagnostic only</t>
         </is>
       </c>
     </row>
@@ -1075,39 +1588,31 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- **R² gap in ST2 implementation (0.70-0.98 vs implied &gt;0.90)**: gap is driven by scalar λ_m and GO−V* surplus error, not by a real failure of the labor theory of value</t>
+          <t>- Note: v0 ST2-era implementation R² 0.70–0.98 was driven by scalar-λ_m + GO−V* surplus error in the proxy, not by a real failure of LTV; v1.1 sector-disaggregated procedure should produce R² consistent with the consistent-procedure framework</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: drives single-year R² outliers; likely IO data gap; not yet diagnosed</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Only 6 benchmark years available**: small cross-section limits regression robustness even when the real fix is implemented</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>- **Sector-level value-added decomposition (ST 1994 §4.2 pp.86-88) not yet implemented**: current code uses aggregate scalar ratio</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- **Book R²&gt;0.95 attribution unverified**: prior research files assert this but direct re-read of Ch7 finds no such literal claim; the load-bearing book number is Khanjian's 6-9%, not 95%</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: propagates from upstream S701/S702.</t>
         </is>
       </c>
     </row>
@@ -1115,95 +1620,135 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- **CH7_REAL_FIX_PLAN.md not yet authored** — flagged here as "to be authored alongside Stage 5 real-fix sub-stage"</t>
+          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: propagates from upstream.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>- **Small cross-section (6 SIC + 4 NAICS benchmark years × 8 productive sectors)**: R² should be interpreted cautiously; aggregate Khanjian deviation magnitude is the load-bearing test.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **1963 benchmark anomaly (WARN-03)**: may propagate from upstream IO data gap; if observed in V03, document as known_issue rather than re-introducing proxy.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- **Book R²&gt;0.95 attribution unverified**: prior research files assert R²&gt;0.95; direct Ch7 re-read finds no such literal claim. Load-bearing book number is Khanjian's 6–9% S*/V*, not 95% R².</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- Upstream: S701 (labor values), S702 (prices of production), S513 (Marxian profit rate)</t>
+          <t>- **Sector-level value-added decomposition (ST 1994 §4.2 pp.86-88)**: handled inside upstream S701/S702 v1.1 implementations; S703 inherits the disaggregated form.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>- Downstream: none (S703 is the empirical test endpoint of the Ch7 framework)</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- Related external: Khanjian (1988, 1989), Wolff (1977a/b, 1979, 1987), Sharpe (1982); the book's Ch7 §7.4 cross-study critique</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>- Project artifact: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` (to be authored); WARN-03 1963 diagnosis</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>- Upstream: **S701 (real labor values — v1.1)**, **S702 (real prices of production — v1.1)**, S513 (Marxian profit rate)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- Downstream: none (S703 is the empirical test endpoint of the Ch7 framework)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- Related external: Khanjian (1988, 1989), Wolff (1977a/b, 1979, 1987), Sharpe (1982); ST 1994 Ch7 §7.4 cross-study critique</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S703_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`; WARN-03 1963 diagnosis (pending)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 11/25/33/34/36 cited via research JSON + registry entry + project CLAUDE.md proxy-disclosure mandate</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1988,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[internal-decision-record]; NickyData/data/final-data/book/series/S701.csv; NickyData/data/final-data/book/series/S702.csv; ASSUMPTIONS.md ASM-M-002</t>
+          <t>[internal-decision-record]; AnuData/data/final-data/book/series/S701.csv; AnuData/data/final-data/book/series/S702.csv; ASSUMPTIONS.md ASM-M-002</t>
         </is>
       </c>
     </row>
@@ -1693,10 +2238,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1751,7 +2296,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PROXY CONSTRUCTION NOTICE</t>
+          <t>EXTENSION</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -1762,94 +2307,189 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>BLS+BEA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proxy_basis</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>&lt;not specified&gt;</t>
+          <t>1977</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>proxy_disclosure</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Series is a proxy, not a direct replication. See DPR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S703-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTENSION</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>null - series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>S703-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>extension_period</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[1990, 2024]</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.3).", "extension_source": "Derived from S701/S702 difference indicator (extended via the same upstream extensions)", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"1947": 37.77029651566801, "1958": 37.72037297739869, "1963": 41.520206844914256, "1967": 41.78590608470474, "1972": 37.77669655367616, "1977": 35.53064371634139}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>[0.0, 100.0]</t>
-        </is>
-      </c>
-    </row>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"1967": -66.579797, "1972": -70.224955, "1977": -73.053206, "1990": -75.817058, "2024": -80.614159}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[587.2274, 1204.0621]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reference values reflect the v1.2 Iter 2 output-weighted per-partition aggregate deviation. Magnitudes are structurally large (-66% to -81%) because the formula compares two disjoint sector partitions (productive vs unproductive labor coefficients), NOT the value-vs-price-form S/V rates the Khanjian 6%-9% benchmark addresses. The proxy:true flag is retained; the formula is the closest valid implementation of the v1.2 plan B.1 'per-sector deviation weighted by gross output share' specification given the S701/S702 partition design, but it does NOT measure the price-value deviation phenomenon the book's Ch7 7.3-7.4 narrative describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>percent_series_proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[1972, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S703.xlsx
+++ b/extenbooks/S703.xlsx
@@ -450,7 +450,7 @@
   <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S703 — Value-Price Deviations</t>
+          <t>S703 — Productive/Unproductive Labor-Coefficient Partition Gap</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -505,10 +505,10 @@
         <v>1967</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-66.57979683368896</v>
+        <v>-65.01432080867077</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>-66.57979683368896</v>
+        <v>-65.01432080867077</v>
       </c>
       <c r="D3" s="3" t="n">
         <v/>
@@ -519,10 +519,10 @@
         <v>1972</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-70.22495543814489</v>
+        <v>-23.85225590539053</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-70.22495543814489</v>
+        <v>-23.85225590539053</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
@@ -533,10 +533,10 @@
         <v>1977</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-73.05320596603123</v>
+        <v>-17.64431579226428</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-73.05320596603123</v>
+        <v>-17.64431579226428</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
@@ -550,10 +550,10 @@
         <v/>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-75.81705754778557</v>
+        <v>-19.84837209302293</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-75.81705754778557</v>
+        <v>-19.84837209302293</v>
       </c>
     </row>
     <row r="7">
@@ -564,10 +564,10 @@
         <v/>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-75.87627630063004</v>
+        <v>-22.43029880627472</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-75.87627630063004</v>
+        <v>-22.43029880627472</v>
       </c>
     </row>
     <row r="8">
@@ -578,10 +578,10 @@
         <v/>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-75.85810335957103</v>
+        <v>-23.11723622389008</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-75.85810335957103</v>
+        <v>-23.11723622389008</v>
       </c>
     </row>
     <row r="9">
@@ -592,10 +592,10 @@
         <v/>
       </c>
       <c r="C9" s="3" t="n">
-        <v>-75.94073370266663</v>
+        <v>-23.48824272731262</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-75.94073370266663</v>
+        <v>-23.48824272731262</v>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v/>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-76.14499963452754</v>
+        <v>-22.35662846283561</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-76.14499963452754</v>
+        <v>-22.35662846283561</v>
       </c>
     </row>
     <row r="11">
@@ -620,10 +620,10 @@
         <v/>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-76.51253935478702</v>
+        <v>-21.83843254349224</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-76.51253935478702</v>
+        <v>-21.83843254349224</v>
       </c>
     </row>
     <row r="12">
@@ -634,10 +634,10 @@
         <v/>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-76.69317803046162</v>
+        <v>-21.84331229213248</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-76.69317803046162</v>
+        <v>-21.84331229213248</v>
       </c>
     </row>
     <row r="13">
@@ -648,10 +648,10 @@
         <v/>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-76.78595994657277</v>
+        <v>5.987349192835565</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-76.78595994657277</v>
+        <v>5.987349192835565</v>
       </c>
     </row>
     <row r="14">
@@ -662,10 +662,10 @@
         <v/>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-76.70304576170466</v>
+        <v>3.618285739657237</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-76.70304576170466</v>
+        <v>3.618285739657237</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         <v/>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-76.5619511165565</v>
+        <v>2.910656471964941</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-76.5619511165565</v>
+        <v>2.910656471964941</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +690,10 @@
         <v/>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-76.90897819315325</v>
+        <v>2.573159551330515</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-76.90897819315325</v>
+        <v>2.573159551330515</v>
       </c>
     </row>
     <row r="17">
@@ -704,10 +704,10 @@
         <v/>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-76.95984863932946</v>
+        <v>2.817642859000175</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-76.95984863932946</v>
+        <v>2.817642859000175</v>
       </c>
     </row>
     <row r="18">
@@ -718,10 +718,10 @@
         <v/>
       </c>
       <c r="C18" s="3" t="n">
-        <v>-76.48856120883886</v>
+        <v>4.832660971896209</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-76.48856120883886</v>
+        <v>4.832660971896209</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v/>
       </c>
       <c r="C19" s="3" t="n">
-        <v>-76.27274568974205</v>
+        <v>4.433706005544647</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-76.27274568974205</v>
+        <v>4.433706005544647</v>
       </c>
     </row>
     <row r="20">
@@ -746,10 +746,10 @@
         <v/>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-76.57736033912896</v>
+        <v>3.790604965828531</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-76.57736033912896</v>
+        <v>3.790604965828531</v>
       </c>
     </row>
     <row r="21">
@@ -760,10 +760,10 @@
         <v/>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-76.836732033088</v>
+        <v>5.364094557556647</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-76.836732033088</v>
+        <v>5.364094557556647</v>
       </c>
     </row>
     <row r="22">
@@ -774,10 +774,10 @@
         <v/>
       </c>
       <c r="C22" s="3" t="n">
-        <v>-77.12039557550665</v>
+        <v>6.361275598699192</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-77.12039557550665</v>
+        <v>6.361275598699192</v>
       </c>
     </row>
     <row r="23">
@@ -788,10 +788,10 @@
         <v/>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-77.16677353425693</v>
+        <v>9.3331676368453</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-77.16677353425693</v>
+        <v>9.3331676368453</v>
       </c>
     </row>
     <row r="24">
@@ -802,10 +802,10 @@
         <v/>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-77.2586954182395</v>
+        <v>13.64267233765397</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-77.2586954182395</v>
+        <v>13.64267233765397</v>
       </c>
     </row>
     <row r="25">
@@ -816,10 +816,10 @@
         <v/>
       </c>
       <c r="C25" s="3" t="n">
-        <v>-76.44613475528043</v>
+        <v>9.965797406207296</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-76.44613475528043</v>
+        <v>9.965797406207296</v>
       </c>
     </row>
     <row r="26">
@@ -830,10 +830,10 @@
         <v/>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-76.16159166835824</v>
+        <v>12.08583209749484</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-76.16159166835824</v>
+        <v>12.08583209749484</v>
       </c>
     </row>
     <row r="27">
@@ -844,10 +844,10 @@
         <v/>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-76.50870872316462</v>
+        <v>15.16813949322051</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-76.50870872316462</v>
+        <v>15.16813949322051</v>
       </c>
     </row>
     <row r="28">
@@ -858,10 +858,10 @@
         <v/>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-76.72370779920013</v>
+        <v>10.41890308255608</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-76.72370779920013</v>
+        <v>10.41890308255608</v>
       </c>
     </row>
     <row r="29">
@@ -872,10 +872,10 @@
         <v/>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-76.88025728166258</v>
+        <v>9.332632795482686</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-76.88025728166258</v>
+        <v>9.332632795482686</v>
       </c>
     </row>
     <row r="30">
@@ -886,10 +886,10 @@
         <v/>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-77.21071331496849</v>
+        <v>6.77702167116703</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-77.21071331496849</v>
+        <v>6.77702167116703</v>
       </c>
     </row>
     <row r="31">
@@ -900,10 +900,10 @@
         <v/>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-77.30994877458866</v>
+        <v>-0.0842067400127193</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-77.30994877458866</v>
+        <v>-0.0842067400127193</v>
       </c>
     </row>
     <row r="32">
@@ -914,10 +914,10 @@
         <v/>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-77.33678016133159</v>
+        <v>-3.297611230743399</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-77.33678016133159</v>
+        <v>-3.297611230743399</v>
       </c>
     </row>
     <row r="33">
@@ -928,10 +928,10 @@
         <v/>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-77.54479663202198</v>
+        <v>-0.0049235487250045</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-77.54479663202198</v>
+        <v>-0.0049235487250045</v>
       </c>
     </row>
     <row r="34">
@@ -942,10 +942,10 @@
         <v/>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-78.15106457725179</v>
+        <v>-0.7215752460055408</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-78.15106457725179</v>
+        <v>-0.7215752460055408</v>
       </c>
     </row>
     <row r="35">
@@ -956,10 +956,10 @@
         <v/>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-78.58800473957413</v>
+        <v>-3.494754098508856</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-78.58800473957413</v>
+        <v>-3.494754098508856</v>
       </c>
     </row>
     <row r="36">
@@ -970,10 +970,10 @@
         <v/>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-77.39133492145925</v>
+        <v>-7.158403665721057</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-77.39133492145925</v>
+        <v>-7.158403665721057</v>
       </c>
     </row>
     <row r="37">
@@ -984,10 +984,10 @@
         <v/>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-78.01836107779499</v>
+        <v>-5.126784868471427</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-78.01836107779499</v>
+        <v>-5.126784868471427</v>
       </c>
     </row>
     <row r="38">
@@ -998,10 +998,10 @@
         <v/>
       </c>
       <c r="C38" s="3" t="n">
-        <v>-79.19893212918043</v>
+        <v>-2.415729028204125</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>-79.19893212918043</v>
+        <v>-2.415729028204125</v>
       </c>
     </row>
     <row r="39">
@@ -1012,10 +1012,10 @@
         <v/>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-80.09440933906036</v>
+        <v>-6.26852006208831</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-80.09440933906036</v>
+        <v>-6.26852006208831</v>
       </c>
     </row>
     <row r="40">
@@ -1026,10 +1026,10 @@
         <v/>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-80.61415861348353</v>
+        <v>-8.40254236799891</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-80.61415861348353</v>
+        <v>-8.40254236799891</v>
       </c>
     </row>
   </sheetData>
@@ -1043,10 +1043,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Value-Price Deviations</t>
+          <t>Productive/Unproductive Labor-Coefficient Partition Gap</t>
         </is>
       </c>
     </row>
@@ -1102,11 +1102,6 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>Book Table</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7.3</t>
         </is>
       </c>
     </row>
@@ -1210,217 +1205,222 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Subseries</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>source / role</t>
-        </is>
-      </c>
+          <t>PROXY DISCLOSURE</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S703-A</t>
+          <t>proxy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
+          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S703-EXT</t>
+          <t>proxy_basis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BLS CES + BEA</t>
+          <t>&lt;not specified&gt;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S703-COMBINED</t>
+          <t>proxy_disclosure</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S&amp;T 1994 + BLS/BEA</t>
+          <t>Matrix-derived or surrogate construction; consult docs/series/S703_DPR.md for full disclosure.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S703-A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S703-EXT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BLS CES + BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S703-COMBINED</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 + BLS/BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S703 — Value-Price Deviations (real, consistent-procedure regression)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## Series</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>- **SID**: S703</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- **Name**: Value-Price Deviations (Chapter 7 consistent-procedure regression; real implementation v1.1)</t>
+          <t># S703 — Value-Price Deviations (real, consistent-procedure regression)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>- **Chapter**: 7; registry `book_table` label "7.3" is project-internal — the book has no literal Table 7.3. The empirical anchor is Khanjian (1989) 6–9% S*/V* deviation reported in **Ch. 7 §7.3** (p.223) and the consistent-procedure framework in **Ch. 4 §4.1** Tables 4.1–4.3</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **Status**: validated_book_and_extension</t>
+          <t>## Series</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Units**: percent (aggregate S*/V* deviation between price and value forms); also reports per-year R² from cross-sectional regression</t>
+          <t>- **SID**: S703</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>- **Name**: Value-Price Deviations (Chapter 7 consistent-procedure regression; real implementation v1.1)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
+          <t>- **Chapter**: 7; registry `book_table` label "7.3" is project-internal — the book has no literal Table 7.3. The empirical anchor is Khanjian (1989) 6–9% S*/V* deviation reported in **Ch. 7 §7.3** (p.223) and the consistent-procedure framework in **Ch. 4 §4.1** Tables 4.1–4.3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>- **Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S703 implements the book's consistent-procedure cross-sectional regression per ST 1994 Ch4 §4.1 + Ch7 §7.3 (p.223). The v1.0 percent-deviation scalar `(S702 - S701)/S701 * 100` (which was algebraically identical to S513 * 100 — see DIV-011 supersession note) has been retired. With both S701 and S702 now real and sector-disaggregated in v1.1, the book's empirical test is performed for the first time.</t>
+          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>- **Units**: percent (aggregate S*/V* deviation between price and value forms); also reports per-year R² from cross-sectional regression</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Procedure (per `Technical/code/P02_processors/P02_S703_value_price_deviations.py`, v1.1 rewrite):</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>per benchmark year y:</t>
+          <t>S703 implements the book's consistent-procedure cross-sectional regression per ST 1994 Ch4 §4.1 + Ch7 §7.3 (p.223). The v1.0 percent-deviation scalar `(S702 - S701)/S701 * 100` (which was algebraically identical to S513 * 100 — see DIV-011 supersession note) has been retired. With both S701 and S702 now real and sector-disaggregated in v1.1, the book's empirical test is performed for the first time.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  log(lambda*_j) ~ a_y + b_y * log(pp*_j)        # cross-sectional OLS across 8 ST productive sectors</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  R²_y = goodness of fit</t>
+          <t>Procedure (per `Technical/code/P02_processors/P02_S703_value_price_deviations.py`, v1.1 rewrite):</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S*/V*_value(y), S*/V*_price(y) = aggregate rates of surplus value, value and price forms</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  deviation_pct(y) = |S*/V*_price(y) - S*/V*_value(y)| / S*/V*_value(y) * 100</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1428,159 +1428,159 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>per benchmark year y:</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  log(lambda*_j) ~ a_y + b_y * log(pp*_j)        # cross-sectional OLS across 8 ST productive sectors</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Khanjian (1989) 6–9% S*/V* envelope (ST 1994 Ch7 §7.3 p.223) is the load-bearing PASS/FAIL anchor; R² is a secondary diagnostic with small-cross-section caveats (8 productive sectors per benchmark year).</t>
+          <t xml:space="preserve">  R²_y = goodness of fit</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  S*/V*_value(y), S*/V*_price(y) = aggregate rates of surplus value, value and price forms</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t xml:space="preserve">  deviation_pct(y) = |S*/V*_price(y) - S*/V*_value(y)| / S*/V*_value(y) * 100</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>- **L01 + P02 (real implementation)**: real S701 + S702 upstream (v1.1); `Technical/code/P02_processors/P02_S703_value_price_deviations.py` (v1.1 rewrite, runs cross-sectional regression and computes Khanjian-style aggregate deviation)</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- **No new external data fetches required** — S703 is a pure regression on real upstream sector vectors</t>
+          <t>The Khanjian (1989) 6–9% S*/V* envelope (ST 1994 Ch7 §7.3 p.223) is the load-bearing PASS/FAIL anchor; R² is a secondary diagnostic with small-cross-section caveats (8 productive sectors per benchmark year).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>- **External comparator**: Khanjian (1989) "The Empirical Evidence Relating to the Existence of Prices of Production: A Critique of Wolff," *Review of Radical Political Economics*; serves as V03_S703 anchor</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 Tables 4.1-4.3 — consistent/inconsistent procedure); `chunk_25/full_transcription.md` (Ch7 §7.3–§7.4 — Khanjian 6–9%, Wolff 12–15% bias); `chunk_33/full_transcription.md` (Appendix G V* methodology); `chunk_34/full_transcription.md` (Appendix G Table G.2 V* formulas); `chunk_36/full_transcription.md` (Appendix J C*/TP* stability)</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>- **Book tables**: Ch4 §4.1 Tables 4.1, 4.2 (consistent procedure worked examples); Table 4.3 (inconsistent symmetric-treatment diagnosis); §5.10 Table 5.12, Figure 5.25 (Khanjian comparison)</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- **Upstream series**: **S701 (real lambda* — v1.1)**, **S702 (real pp* — v1.1)**, S513 (Marxian profit rate r_bar, used in S702)</t>
+          <t>- **L01 + P02 (real implementation)**: real S701 + S702 upstream (v1.1); `Technical/code/P02_processors/P02_S703_value_price_deviations.py` (v1.1 rewrite, runs cross-sectional regression and computes Khanjian-style aggregate deviation)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- **No new external data fetches required** — S703 is a pure regression on real upstream sector vectors</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>## Reference values</t>
+          <t>- **External comparator**: Khanjian (1989) "The Empirical Evidence Relating to the Existence of Prices of Production: A Critique of Wolff," *Review of Radical Political Economics*; serves as V03_S703 anchor</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 Tables 4.1-4.3 — consistent/inconsistent procedure); `chunk_25/full_transcription.md` (Ch7 §7.3–§7.4 — Khanjian 6–9%, Wolff 12–15% bias); `chunk_33/full_transcription.md` (Appendix G V* methodology); `chunk_34/full_transcription.md` (Appendix G Table G.2 V* formulas); `chunk_36/full_transcription.md` (Appendix J C*/TP* stability)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coordinator backfills from `Technical/chopped/S703.csv` after agents 1-3 commit P02_S703 rewrite and `O01_generate_chopped.py` regenerates chopped output.</t>
+          <t>- **Book tables**: Ch4 §4.1 Tables 4.1, 4.2 (consistent procedure worked examples); Table 4.3 (inconsistent symmetric-treatment diagnosis); §5.10 Table 5.12, Figure 5.25 (Khanjian comparison)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- **Upstream series**: **S701 (real lambda* — v1.1)**, **S702 (real pp* — v1.1)**, S513 (Marxian profit rate r_bar, used in S702)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>- Extension years (NAICS): 1997, 2002, 2007, 2012 (per upstream S701/S702 NAICS benchmark availability)</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>- **Khanjian benchmark**: 6–9% S*/V* deviation between price and value forms (ST 1994 Ch7 §7.3 p.223) — primary PASS/FAIL anchor</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- **Wolff comparator**: 12–15% upper envelope (sum of Wolff 4–8% inconsistent-procedure bias + Khanjian 6–9% baseline)</t>
+          <t>Coordinator backfills from `Technical/chopped/S703.csv` after agents 1-3 commit P02_S703 rewrite and `O01_generate_chopped.py` regenerates chopped output.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>- v1.1 `expected_range` tightened to `[0.0, 15.0]` (vs v1.0 proxy's `[0.0, 100.0]` that had to accept matrix-artifact range)</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- Book does NOT literally claim R² &gt; 0.95 (prior research-file attribution flagged for re-verification); R² treated as secondary diagnostic only</t>
+          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -1588,31 +1588,39 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- Note: v0 ST2-era implementation R² 0.70–0.98 was driven by scalar-λ_m + GO−V* surplus error in the proxy, not by a real failure of LTV; v1.1 sector-disaggregated procedure should produce R² consistent with the consistent-procedure framework</t>
+          <t>- Extension years (NAICS): 1997, 2002, 2007, 2012 (per upstream S701/S702 NAICS benchmark availability)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- **Khanjian benchmark**: 6–9% S*/V* deviation between price and value forms (ST 1994 Ch7 §7.3 p.223) — primary PASS/FAIL anchor</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>- **Wolff comparator**: 12–15% upper envelope (sum of Wolff 4–8% inconsistent-procedure bias + Khanjian 6–9% baseline)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- v1.1 `expected_range` tightened to `[0.0, 15.0]` (vs v1.0 proxy's `[0.0, 100.0]` that had to accept matrix-artifact range)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: propagates from upstream S701/S702.</t>
+          <t>- Book does NOT literally claim R² &gt; 0.95 (prior research-file attribution flagged for re-verification); R² treated as secondary diagnostic only</t>
         </is>
       </c>
     </row>
@@ -1620,63 +1628,63 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: propagates from upstream.</t>
+          <t>- Note: v0 ST2-era implementation R² 0.70–0.98 was driven by scalar-λ_m + GO−V* surplus error in the proxy, not by a real failure of LTV; v1.1 sector-disaggregated procedure should produce R² consistent with the consistent-procedure framework</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>- **Small cross-section (6 SIC + 4 NAICS benchmark years × 8 productive sectors)**: R² should be interpreted cautiously; aggregate Khanjian deviation magnitude is the load-bearing test.</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: may propagate from upstream IO data gap; if observed in V03, document as known_issue rather than re-introducing proxy.</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>- **Book R²&gt;0.95 attribution unverified**: prior research files assert R²&gt;0.95; direct Ch7 re-read finds no such literal claim. Load-bearing book number is Khanjian's 6–9% S*/V*, not 95% R².</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **Sector-level value-added decomposition (ST 1994 §4.2 pp.86-88)**: handled inside upstream S701/S702 v1.1 implementations; S703 inherits the disaggregated form.</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: propagates from upstream S701/S702.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: propagates from upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **Small cross-section (6 SIC + 4 NAICS benchmark years × 8 productive sectors)**: R² should be interpreted cautiously; aggregate Khanjian deviation magnitude is the load-bearing test.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- **1963 benchmark anomaly (WARN-03)**: may propagate from upstream IO data gap; if observed in V03, document as known_issue rather than re-introducing proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>- Upstream: **S701 (real labor values — v1.1)**, **S702 (real prices of production — v1.1)**, S513 (Marxian profit rate)</t>
+          <t>- **Book R²&gt;0.95 attribution unverified**: prior research files assert R²&gt;0.95; direct Ch7 re-read finds no such literal claim. Load-bearing book number is Khanjian's 6–9% S*/V*, not 95% R².</t>
         </is>
       </c>
     </row>
@@ -1684,23 +1692,19 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>- Downstream: none (S703 is the empirical test endpoint of the Ch7 framework)</t>
+          <t>- **Sector-level value-added decomposition (ST 1994 §4.2 pp.86-88)**: handled inside upstream S701/S702 v1.1 implementations; S703 inherits the disaggregated form.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>- Related external: Khanjian (1988, 1989), Wolff (1977a/b, 1979, 1987), Sharpe (1982); ST 1994 Ch7 §7.4 cross-study critique</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S703_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`; WARN-03 1963 diagnosis (pending)</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
@@ -1712,19 +1716,23 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- Upstream: **S701 (real labor values — v1.1)**, **S702 (real prices of production — v1.1)**, S513 (Marxian profit rate)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- Downstream: none (S703 is the empirical test endpoint of the Ch7 framework)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+          <t>- Related external: Khanjian (1988, 1989), Wolff (1977a/b, 1979, 1987), Sharpe (1982); ST 1994 Ch7 §7.4 cross-study critique</t>
         </is>
       </c>
     </row>
@@ -1732,21 +1740,53 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S703_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`; WARN-03 1963 diagnosis (pending)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
@@ -2238,10 +2278,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2296,7 +2336,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EXTENSION</t>
+          <t>PROXY CONSTRUCTION NOTICE</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -2307,187 +2347,235 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>proxy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BLS+BEA</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>proxy_basis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>&lt;not specified&gt;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>proxy_disclosure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>derive</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>output_subseries</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>S703-EXT</t>
-        </is>
-      </c>
-    </row>
+          <t>Series is a proxy, not a direct replication. See DPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>combined_subseries</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>S703-COMBINED</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>extension_period</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1990, 2024]</t>
+          <t>BLS+BEA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.3).", "extension_source": "Derived from S701/S702 difference indicator (extended via the same upstream extensions)", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
+          <t>1977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S703-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S703-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>extension_period</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"1967": -66.579797, "1972": -70.224955, "1977": -73.053206, "1990": -75.817058, "2024": -80.614159}</t>
+          <t>[1990, 2024]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[587.2274, 1204.0621]</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.3).", "extension_source": "Derived from S701/S702 difference indicator (extended via the same upstream extensions)", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-    </row>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Reference values reflect the v1.2 Iter 2 output-weighted per-partition aggregate deviation. Magnitudes are structurally large (-66% to -81%) because the formula compares two disjoint sector partitions (productive vs unproductive labor coefficients), NOT the value-vs-price-form S/V rates the Khanjian 6%-9% benchmark addresses. The proxy:true flag is retained; the formula is the closest valid implementation of the v1.2 plan B.1 'per-sector deviation weighted by gross output share' specification given the S701/S702 partition design, but it does NOT measure the price-value deviation phenomenon the book's Ch7 7.3-7.4 narrative describes.</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>percent_series_proxy</t>
+          <t>{"1967": -65.014321, "1977": -17.644316, "1990": -19.848372, "2024": -8.402542}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[-100.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tolerance</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Output-weighted partition gap on the rebuilt cache. MUCH smaller than the defective-cache -66..-81% and sign-varying; NEVER validate against the Khanjian 6-9% band (different concept — DIV-038). 1997 method-change overlap: SIC-path -21.82% vs NAICS-path +5.99% (scale-free series left unspliced; both values in provenance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>extension_year_range</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>[1972, 2024]</t>
         </is>

--- a/extenbooks/S703.xlsx
+++ b/extenbooks/S703.xlsx
@@ -1628,7 +1628,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- Note: v0 ST2-era implementation R² 0.70–0.98 was driven by scalar-λ_m + GO−V* surplus error in the proxy, not by a real failure of LTV; v1.1 sector-disaggregated procedure should produce R² consistent with the consistent-procedure framework</t>
+          <t>- Note: v0 predecessor-build-era implementation R² 0.70–0.98 was driven by scalar-λ_m + GO−V* surplus error in the proxy, not by a real failure of LTV; v1.1 sector-disaggregated procedure should produce R² consistent with the consistent-procedure framework</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+          <t>- **Original research**: `Technical/research/S703_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T703_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Correct computation of S703 requires that labor values and prices of production be expressed in commensurable units before regression. Labor values λ* are in hours per dollar of gross output; prices of production in money terms are in dollars. The conversion uses the labor value of money λ_m = total productive hours / total value added. Money compensation v_j is converted to labor-value compensation v_j_labor = v_j × λ_m before computing pp*_j. The initial ST2 implementation omitted this conversion, producing R² = 0.003–0.035 and MAD &gt; 31,000%. After applying the λ_m conversion, MAD improved to 72–87% but R² remained low (0.003–0.035), indicating a residual methodological issue: surplus was computed from gross output minus V* rather than value added minus V*, contrary to the book's Section 4.2 (pp. 86–88) sector-level value-added decomposition.</t>
+          <t>Correct computation of S703 requires that labor values and prices of production be expressed in commensurable units before regression. Labor values λ* are in hours per dollar of gross output; prices of production in money terms are in dollars. The conversion uses the labor value of money λ_m = total productive hours / total value added. Money compensation v_j is converted to labor-value compensation v_j_labor = v_j × λ_m before computing pp*_j. The initial predecessor-build implementation omitted this conversion, producing R² = 0.003–0.035 and MAD &gt; 31,000%. After applying the λ_m conversion, MAD improved to 72–87% but R² remained low (0.003–0.035), indicating a residual methodological issue: surplus was computed from gross output minus V* rather than value added minus V*, contrary to the book's Section 4.2 (pp. 86–88) sector-level value-added decomposition.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Current ST2 implementation achieves R² = 0.70–0.98 (varies by benchmark year) versus the book's claim of R² &gt; 0.95. The gap is caused by: (a) scalar rather than sector-level λ_m application — the book requires computing c_j and v_j in labor-value units sector by sector, not applying a single aggregate ratio; (b) incorrect surplus computation using GO − V* instead of VA − V* in the profit-rate equalization step; (c) the 1963 benchmark anomaly (WARN-03) where S702 collapses to near-zero values, likely reflecting a data gap in the underlying IO table rather than a true economic reading. Resolution is deferred to Wave 2, pending a dedicated sector-level value-added decomposition pass and diagnosis of the 1963 IO data.</t>
+          <t>Current predecessor-build implementation achieves R² = 0.70–0.98 (varies by benchmark year) versus the book's claim of R² &gt; 0.95. The gap is caused by: (a) scalar rather than sector-level λ_m application — the book requires computing c_j and v_j in labor-value units sector by sector, not applying a single aggregate ratio; (b) incorrect surplus computation using GO − V* instead of VA − V* in the profit-rate equalization step; (c) the 1963 benchmark anomaly (WARN-03) where S702 collapses to near-zero values, likely reflecting a data gap in the underlying IO table rather than a true economic reading. Resolution is deferred to Wave 2, pending a dedicated sector-level value-added decomposition pass and diagnosis of the 1963 IO data.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
